--- a/documentacao-e-dados-auxiliares/backlog.xlsx
+++ b/documentacao-e-dados-auxiliares/backlog.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Biblioteca\projetos\sistema-resgistro-analise-integrada\documentacao-e-dados-auxiliares\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Biblioteca\sistema-resgistro-analise-integrada\documentacao-e-dados-auxiliares\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D216185C-CA59-43E5-8273-5775F50FC894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB66047D-E524-4B15-B9EC-4C542301CC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sprint 1" sheetId="2" r:id="rId2"/>
+    <sheet name="Backlog" sheetId="1" r:id="rId1"/>
+    <sheet name="Validação" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="70">
   <si>
     <t>Item</t>
   </si>
@@ -151,9 +151,6 @@
     <t>Visual do sistema</t>
   </si>
   <si>
-    <t>BACKLOG SPRINT 1</t>
-  </si>
-  <si>
     <t>Formulário de Entrevistas - Animais Vivos</t>
   </si>
   <si>
@@ -227,13 +224,25 @@
   </si>
   <si>
     <t>Form. Castrações</t>
+  </si>
+  <si>
+    <t>Etapa</t>
+  </si>
+  <si>
+    <t>Form. Hemograma/Bioquímico</t>
+  </si>
+  <si>
+    <t>Form. Resultados QPCR e CPCR</t>
+  </si>
+  <si>
+    <t>Forn. Entrevistas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,16 +258,8 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -275,12 +276,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor rgb="FFFFFF38"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -308,17 +303,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,18 +410,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabela13" displayName="Tabela13" ref="A2:D9" totalsRowShown="0">
-  <autoFilter ref="A2:D9" xr:uid="{00000000-0009-0000-0100-000002000000}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Item"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Tipo"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Complexidade"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Risco"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3B8A1BAF-77FB-421B-8D4C-103CD9F6C3B0}" name="Tabela13" displayName="Tabela13" ref="A1:E57" totalsRowShown="0">
+  <autoFilter ref="A1:E57" xr:uid="{3B8A1BAF-77FB-421B-8D4C-103CD9F6C3B0}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{B7956BD4-B61A-40A5-BFC4-76E7A235BA87}" name="Item"/>
+    <tableColumn id="2" xr3:uid="{32CC5DED-47E1-4453-A9A4-F42A9877554A}" name="Tipo"/>
+    <tableColumn id="3" xr3:uid="{157424FD-86D8-46AF-A632-1FD4B116E08C}" name="Complexidade"/>
+    <tableColumn id="4" xr3:uid="{15CF01EA-36BB-49CA-822E-46B90316C561}" name="Risco"/>
+    <tableColumn id="5" xr3:uid="{0C7BD54A-2865-4985-8861-DFDA56128ECC}" name="Etapa"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -612,14 +600,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H49"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="34.140625" customWidth="1"/>
-    <col min="2" max="2" width="46.5703125" customWidth="1"/>
-    <col min="3" max="4" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34.125" customWidth="1"/>
+    <col min="2" max="2" width="46.625" customWidth="1"/>
+    <col min="3" max="4" width="18.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -633,7 +621,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -653,7 +641,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -673,7 +661,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -693,7 +681,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -707,7 +695,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -721,334 +709,334 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:8">
+      <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="C7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="C8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="C10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="C11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="C12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="C13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="C14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="C15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="C16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="C17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="C18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C19" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="C19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="C20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C21" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="C21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="C22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="C23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="C24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C25" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="C25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B26" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+      <c r="C28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>11</v>
@@ -1057,26 +1045,26 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="B32" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>6</v>
@@ -1085,12 +1073,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4">
       <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>6</v>
@@ -1099,12 +1087,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4">
       <c r="A34" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>11</v>
@@ -1113,96 +1101,96 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4">
       <c r="A35" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+      <c r="B36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
+      <c r="B38" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="B41" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>11</v>
@@ -1211,12 +1199,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4">
       <c r="A42" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>6</v>
@@ -1225,82 +1213,82 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4">
       <c r="A43" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
+      <c r="B45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+      <c r="B47" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="B48" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>11</v>
@@ -1309,7 +1297,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4">
       <c r="A49" s="3" t="s">
         <v>39</v>
       </c>
@@ -1343,151 +1331,660 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33BCBB25-27D5-48AC-ACFD-F5B31D91C842}">
+  <dimension ref="A1:I54"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="34.140625" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" customWidth="1"/>
-    <col min="3" max="4" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34.125" customWidth="1"/>
+    <col min="2" max="2" width="46.625" customWidth="1"/>
+    <col min="3" max="4" width="18.75" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:9" ht="16.5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="6">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B54" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
+      <c r="C54" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D8" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>$H$3:$H$5</formula1>
-      <formula2>0</formula2>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9:C1048576 C1:C7" xr:uid="{DEF784A0-155A-4E05-B7A7-59A3DF8CEAA6}">
+      <formula1>$H$2:$H$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C8" xr:uid="{00000000-0002-0000-0100-000001000000}">
-      <formula1>$G$3:$G$5</formula1>
-      <formula2>0</formula2>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9:D1048576 D1:D7" xr:uid="{AA571BDA-A057-49D7-ACD6-B2A911C86A90}">
+      <formula1>$I$2:$I$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
